--- a/lead-enquiries.xlsx
+++ b/lead-enquiries.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -699,9 +699,109 @@
         <v>2026-06-23T15:34:27.499Z</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>LEAD-1001</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Test User</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Google</v>
+      </c>
+      <c r="D7" t="str">
+        <v>test@google.com</v>
+      </c>
+      <c r="E7" t="str">
+        <v>9999999999</v>
+      </c>
+      <c r="F7">
+        <v>50</v>
+      </c>
+      <c r="G7">
+        <v>1500</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Diwali Gifting</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Download Hub</v>
+      </c>
+      <c r="J7" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Catalogue Request</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Verified</v>
+      </c>
+      <c r="M7" t="str">
+        <v>No</v>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v>2026-07-27T12:21:39.839Z</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>LEAD-1002</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Test User</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Google</v>
+      </c>
+      <c r="D8" t="str">
+        <v>test@google.com</v>
+      </c>
+      <c r="E8" t="str">
+        <v>9999999999</v>
+      </c>
+      <c r="F8">
+        <v>50</v>
+      </c>
+      <c r="G8">
+        <v>1500</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Diwali Gifting</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Download Hub</v>
+      </c>
+      <c r="J8" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Catalogue Request</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Suspicious</v>
+      </c>
+      <c r="M8" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="N8" t="str">
+        <v>Duplicate inquiry email within 24h; Duplicate inquiry phone within 24h</v>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v>2026-07-27T12:27:36.379Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/lead-enquiries.xlsx
+++ b/lead-enquiries.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:P9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -799,9 +799,59 @@
         <v>2026-07-27T12:27:36.379Z</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>LEAD-1003</v>
+      </c>
+      <c r="B9" t="str">
+        <v>gghj</v>
+      </c>
+      <c r="C9" t="str">
+        <v>ddd</v>
+      </c>
+      <c r="D9" t="str">
+        <v>company@google.com</v>
+      </c>
+      <c r="E9" t="str">
+        <v>9999999999</v>
+      </c>
+      <c r="F9">
+        <v>50</v>
+      </c>
+      <c r="G9">
+        <v>1500</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Diwali Gifting</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Download Hub</v>
+      </c>
+      <c r="J9" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Catalogue Request</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Suspicious</v>
+      </c>
+      <c r="M9" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="N9" t="str">
+        <v>Duplicate inquiry phone within 24h</v>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v>2026-07-28T11:15:06.220Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P9"/>
   </ignoredErrors>
 </worksheet>
 </file>